--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488140_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488140_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. ROPERO BENIEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3475</v>
+        <v>3.6197</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1025</v>
+        <v>3.3935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.245</v>
+        <v>0.2262</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7177</v>
+        <v>1.0391</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8267</v>
+        <v>0.5583</v>
       </c>
       <c r="I2" t="n">
-        <v>0.891</v>
+        <v>0.4808</v>
       </c>
       <c r="J2" t="n">
-        <v>4.544</v>
+        <v>3.217</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7145</v>
+        <v>1.8378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8294</v>
+        <v>1.3792</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8263</v>
+        <v>-2.178</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8878</v>
+        <v>-1.2796</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0616</v>
+        <v>-0.8984</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3328</v>
+        <v>-0.3644</v>
       </c>
       <c r="T2" t="n">
-        <v>0.485</v>
+        <v>-0.1554</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8478</v>
+        <v>-0.2089</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2589</v>
+        <v>2.2038</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2583</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2589</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ROPERO BENIEZ</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8833</v>
+        <v>2.9239</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0018</v>
+        <v>3.3191</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1185</v>
+        <v>-0.3952</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0391</v>
+        <v>3.7177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5583</v>
+        <v>2.8267</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4808</v>
+        <v>0.891</v>
       </c>
       <c r="J3" t="n">
-        <v>3.217</v>
+        <v>4.544</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8378</v>
+        <v>3.7145</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3792</v>
+        <v>0.8294</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.178</v>
+        <v>-0.8263</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2796</v>
+        <v>-0.8878</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8984</v>
+        <v>0.0616</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1008</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5471</v>
+        <v>-0.2984</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5536</v>
+        <v>0.2076</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2038</v>
+        <v>-1.2589</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2583</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9455</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1998</v>
+        <v>1.9707</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2057</v>
+        <v>1.7663</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0059</v>
+        <v>0.2044</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4696</v>
+        <v>-2.4153</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5565</v>
+        <v>-0.5228</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0261</v>
+        <v>-1.8925</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9717</v>
+        <v>-0.8759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5925</v>
+        <v>0.3563</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3792</v>
+        <v>-1.2322</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5021</v>
+        <v>-1.5394</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.149</v>
+        <v>-0.8791</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3531</v>
+        <v>-0.6603</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.308</v>
+        <v>-0.614</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.766</v>
+        <v>-0.1899</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5419</v>
+        <v>-0.4241</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.1471</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8571</v>
+        <v>1.8372</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0141</v>
+        <v>1.6953</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.157</v>
+        <v>0.1418</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2528</v>
+        <v>0.4696</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9131</v>
+        <v>-0.5565</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6603</v>
+        <v>1.0261</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1462</v>
+        <v>1.9717</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1462</v>
+        <v>0.5925</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.3792</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8934</v>
+        <v>-1.5021</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2331</v>
+        <v>-1.149</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6603</v>
+        <v>-0.3531</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3706</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4823</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6048</v>
+        <v>-0.6706</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2226</v>
+        <v>-0.2764</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8274</v>
+        <v>-0.3942</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.842</v>
+        <v>0.2038</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0808</v>
+        <v>-0.4049</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2388</v>
+        <v>0.6087</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4153</v>
+        <v>-0.1005</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5228</v>
+        <v>-1.102</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8925</v>
+        <v>1.0015</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8759</v>
+        <v>0.0443</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3563</v>
+        <v>-0.5884</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2322</v>
+        <v>0.6327</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5394</v>
+        <v>-0.1448</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8791</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6603</v>
+        <v>0.3687</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7427</v>
+        <v>-0.4368</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8754</v>
+        <v>-0.4492</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8673</v>
+        <v>0.0124</v>
       </c>
       <c r="V6" t="n">
-        <v>3.1471</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1059</v>
+        <v>0.0698</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5028</v>
+        <v>1.9162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6087</v>
+        <v>-1.8464</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1005</v>
+        <v>1.2528</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.102</v>
+        <v>1.9131</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0015</v>
+        <v>-0.6603</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0443</v>
+        <v>3.1462</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5884</v>
+        <v>3.1462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6327</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1448</v>
+        <v>-1.8934</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-1.2331</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3687</v>
+        <v>-0.6603</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5347</v>
+        <v>-0.1825</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5471</v>
+        <v>-0.3205</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0124</v>
+        <v>0.138</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6223</v>
+        <v>-0.7443</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0973</v>
+        <v>-0.2932</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.525</v>
+        <v>-0.4512</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3441</v>
@@ -1078,13 +1078,13 @@
         <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0368</v>
+        <v>-0.0852</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0689</v>
+        <v>0.005</v>
       </c>
       <c r="V8" t="n">
         <v>0.3144</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2201</v>
+        <v>-1.4657</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3484</v>
+        <v>-1.4463</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1283</v>
+        <v>-0.0195</v>
       </c>
       <c r="G9" t="n">
         <v>0.5424</v>
@@ -1156,13 +1156,13 @@
         <v>2.594</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0001</v>
+        <v>-1.2457</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4414</v>
+        <v>-0.5394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5586</v>
+        <v>-0.7064</v>
       </c>
       <c r="V9" t="n">
         <v>2.2022</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8389</v>
+        <v>-2.0845</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.985</v>
+        <v>-1.0829</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8539</v>
+        <v>-1.0016</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2158</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3261</v>
+        <v>-0.5717</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0037</v>
+        <v>-0.1016</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3223</v>
+        <v>-0.4701</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1275</v>
+        <v>-2.1264</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2722</v>
+        <v>-0.468</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8554</v>
+        <v>-1.6584</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6717</v>
@@ -1312,13 +1312,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1736</v>
+        <v>0.1747</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1604</v>
+        <v>-0.0354</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0132</v>
+        <v>0.2101</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8957</v>
+        <v>-2.7918</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0809</v>
+        <v>-1.6121</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8149</v>
+        <v>-1.1797</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2257</v>
+        <v>-1.7105</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8786</v>
+        <v>-1.0486</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6529</v>
+        <v>-0.6619</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0644</v>
+        <v>-1.0295</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0644</v>
+        <v>-0.4596</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.5699</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2901</v>
+        <v>-0.681</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.589</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6529</v>
+        <v>-0.092</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.3053</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2189</v>
+        <v>-0.5826</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6364</v>
+        <v>0.2773</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2589</v>
+        <v>-1.8877</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2589</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9899</v>
+        <v>-2.8711</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4163</v>
+        <v>-1.0809</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5736</v>
+        <v>-1.7902</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7105</v>
+        <v>-0.2257</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0486</v>
+        <v>-0.8786</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6619</v>
+        <v>0.6529</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0295</v>
+        <v>0.0644</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4596</v>
+        <v>0.0644</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5699</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.681</v>
+        <v>-0.2901</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.589</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.092</v>
+        <v>0.6529</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1117</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5034</v>
+        <v>-0.8307</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3867</v>
+        <v>-0.2189</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1167</v>
+        <v>-0.6118</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8877</v>
+        <v>-1.2589</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8877</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.4588</v>
+        <v>-1.458700000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>5.702000000000004</v>
+        <v>5.702099999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.161</v>
+        <v>-7.161100000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3380000000000007</v>
+        <v>0.338000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>0.7978999999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4598999999999999</v>
+        <v>-0.4599</v>
       </c>
       <c r="J14" t="n">
         <v>15.0097</v>
@@ -1546,16 +1546,16 @@
         <v>14.8231</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.223100000000001</v>
+        <v>-5.223000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-3.2578</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9649</v>
+        <v>-1.9651</v>
       </c>
       <c r="V14" t="n">
-        <v>1.573100000000002</v>
+        <v>1.573100000000001</v>
       </c>
       <c r="W14" t="n">
         <v>6.9203</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9561</v>
+        <v>3.3008</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0048</v>
+        <v>3.4381</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0487</v>
+        <v>-0.1373</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2687</v>
+        <v>-1.7586</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3455</v>
+        <v>0.5995</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-2.3581</v>
       </c>
       <c r="J15" t="n">
-        <v>5.621</v>
+        <v>0.3237</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8223</v>
+        <v>2.1981</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7986</v>
+        <v>-1.8744</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3522</v>
+        <v>-2.0824</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4768</v>
+        <v>-1.5987</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8754</v>
+        <v>-0.4837</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.2616</v>
+        <v>1.297</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.5586</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="S15" t="n">
-        <v>3.949</v>
+        <v>0.3003</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6836</v>
+        <v>0.2643</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2654</v>
+        <v>0.036</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3.4621</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2589</v>
+        <v>3.7766</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7849</v>
+        <v>1.5107</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2423</v>
+        <v>2.7317</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4574</v>
+        <v>-1.221</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7586</v>
+        <v>3.2687</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5995</v>
+        <v>3.3455</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3581</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3237</v>
+        <v>5.621</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1981</v>
+        <v>4.8223</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8744</v>
+        <v>0.7986</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0824</v>
+        <v>-2.3522</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5987</v>
+        <v>-1.4768</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4837</v>
+        <v>-0.8754</v>
       </c>
       <c r="P16" t="n">
+        <v>-4.2616</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-5.5586</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.297</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9264</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.2234</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.2156</v>
+        <v>2.5036</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0684</v>
+        <v>1.4105</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.284</v>
+        <v>1.093</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4621</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.7766</v>
+        <v>1.2589</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9423</v>
+        <v>1.4577</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9705</v>
+        <v>1.2643</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0283</v>
+        <v>0.1933</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1256</v>
@@ -1780,13 +1780,13 @@
         <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6183</v>
+        <v>-0.1029</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.2359</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0886</v>
+        <v>0.133</v>
       </c>
       <c r="V17" t="n">
         <v>0.945</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.788</v>
+        <v>1.1266</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8486</v>
+        <v>0.6646</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0606</v>
+        <v>0.462</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9772999999999999</v>
+        <v>-0.0876</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1126</v>
+        <v>-0.3011</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8647</v>
+        <v>0.2135</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1222</v>
+        <v>0.3621</v>
       </c>
       <c r="K18" t="n">
-        <v>0.365</v>
+        <v>0.2791</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7572</v>
+        <v>0.0829</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1448</v>
+        <v>-0.4497</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2524</v>
+        <v>-0.5803</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1076</v>
+        <v>0.1306</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.616</v>
+        <v>0.6022</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2736</v>
+        <v>0.3025</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3425</v>
+        <v>0.2997</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.8619</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8941</v>
+        <v>0.8486</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3613</v>
+        <v>0.0133</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7945</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4544</v>
+        <v>0.1126</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2489</v>
+        <v>0.8647</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3701</v>
+        <v>1.1222</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1169</v>
+        <v>0.365</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.487</v>
+        <v>0.7572</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4244</v>
+        <v>-0.1448</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6626</v>
+        <v>-0.2524</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2381</v>
+        <v>0.1076</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1425</v>
+        <v>-0.5422</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3209</v>
+        <v>-0.2736</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1783</v>
+        <v>-0.2686</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2583</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.315</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3221</v>
+        <v>0.4611</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3221</v>
+        <v>0.5024</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.0412</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3221</v>
+        <v>-1.7945</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3221</v>
+        <v>0.4544</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-2.2489</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3221</v>
+        <v>-0.3701</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3221</v>
+        <v>2.1169</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.487</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-1.4244</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1.6626</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.2381</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.0709</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.0709</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2583</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2687</v>
+        <v>0.3221</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0209</v>
+        <v>0.3221</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2896</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0876</v>
+        <v>0.3221</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3011</v>
+        <v>0.3221</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2135</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3621</v>
+        <v>0.3221</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2791</v>
+        <v>0.3221</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4497</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5803</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2557</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1273</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1079</v>
+        <v>-0.2792</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3865</v>
+        <v>-0.5824</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2786</v>
+        <v>0.3032</v>
       </c>
       <c r="G22" t="n">
         <v>-1.54</v>
@@ -2170,13 +2170,13 @@
         <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6904</v>
+        <v>0.5192</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1269</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5636</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.0005</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0104</v>
+        <v>-1.0596</v>
       </c>
       <c r="E23" t="n">
         <v>0.3801</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3905</v>
+        <v>-1.4397</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0033</v>
@@ -2248,13 +2248,13 @@
         <v>2.2234</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4614</v>
       </c>
       <c r="T23" t="n">
         <v>0.3756</v>
       </c>
       <c r="U23" t="n">
-        <v>0.135</v>
+        <v>0.0858</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8883</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7882</v>
+        <v>-1.5974</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0328</v>
+        <v>-0.9556</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2446</v>
+        <v>-0.6418</v>
       </c>
       <c r="G24" t="n">
         <v>2.0424</v>
@@ -2326,13 +2326,13 @@
         <v>2.0382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6712</v>
+        <v>0.8621</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2373</v>
+        <v>-0.1601</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9085</v>
+        <v>1.0222</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8343</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2294</v>
+        <v>-4.6457</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3763</v>
+        <v>-1.768</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8531</v>
+        <v>-2.8777</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6388</v>
@@ -2404,13 +2404,13 @@
         <v>0.1853</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9647</v>
+        <v>0.5484</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8133</v>
+        <v>0.4216</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1514</v>
+        <v>0.1268</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8877</v>
@@ -2440,19 +2440,19 @@
         <v>1.459000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>6.846</v>
+        <v>6.845900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.3871</v>
+        <v>-5.3869</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3378999999999996</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7975999999999998</v>
+        <v>-0.7975999999999996</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4599000000000006</v>
+        <v>0.4599000000000004</v>
       </c>
       <c r="J26" t="n">
         <v>14.6718</v>
@@ -2482,13 +2482,13 @@
         <v>12.9699</v>
       </c>
       <c r="S26" t="n">
-        <v>5.222799999999999</v>
+        <v>5.223</v>
       </c>
       <c r="T26" t="n">
-        <v>1.965100000000001</v>
+        <v>1.965</v>
       </c>
       <c r="U26" t="n">
-        <v>3.2578</v>
+        <v>3.2579</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5732</v>
